--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Minimum Support Price for Foodgrains According to Crop Year (Fair Average Quality).xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Minimum Support Price for Foodgrains According to Crop Year (Fair Average Quality).xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>Year</t>
   </si>
@@ -34,12 +34,15 @@
     <t>Urad</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-27   </t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025-26   </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -196,27 +199,27 @@
     <t>(Rupees per Quintal)</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :   
-            1. Paddy common : From 1997-98, Minimum Support Price (MSP) is announced for two varieties of paddy -common and Grade ‘A’, as against the 
-                    earlier three categories of common, fine and super fine.
-            2. Wheat prices for 1992-93 and 1993-94, include a Central bonus of `25 per quintal.
-            3. Wheat price for 2006-07 and Paddy common for year 2007-08 include an additional incentive bonus of `100 per quintal is payable over the MSP.
-            4. Wheat prices for 1996-97 includes a Central bonus of `60 per quintal payable up to June 30, 1997.
-            5. Wheat prices for 2005-06 and 2010-11 include a bonus of `50 per quintal payable over the MSP.
-            6. Paddy common for 2006-07 include an additional incentive bonus of `40 per quintal on procurement between October 1, 2006 to March 31, 2007.
-            7. Arhar, Moong and Urad for 2007-08 includes a bonus of  `40 per quintal payable over and above the MSP.
-            8. An additional incentive bonus of  `50 per quintal over the MSP included for paddy common for the years 2008-09 and 2009-10.
-            9. For Arhar, Moong and Urad for 2010-11 and 2011-12 an additional incentive at the rate of ` 500 per quintal payable during the harvest/arrival 
-                    period of two months is included.
-            10. For Arhar, Moong and Urad for 2015-16 and 2017-18 bonus of  `200 per quintal payable over and above the MSP.
-            11. Gram for 2015-16 includes a bonus of ` 75 for quintal and for 2017-18 includes a bonus of ` 150 per quintal on and above MSP and 2016-17
-                  i ncluded a bonus of ` 200 for quintal.
-            12. Arhar, Moong and Urad for 2016-17 includes a bonus of  `425 per quintal over and above MSP.
-Also See Notes on Tables.
-Sources :  
-            1. Ministry of Agriculture, Government of India.
-            2. Commission on Agriculture Costs &amp; Prices (CACP).
-</t>
+    <t xml:space="preserve">Notes   :  1. Paddy common : From 1997-98, Minimum Support Price (MSP) is announced for two varieties of paddy - common and
+                   Grade ‘A’, as against the earlier three categories of common, fine and super fine.
+               2. Wheat prices for 1992-93 and 1993-94, include a Central bonus of ₹ 25 per quintal.
+               3. Wheat price for 2006-07 and Paddy common for year 2007-08 include an additional incentive bonus of ₹ 100 per quintal is
+                  payable over the MSP.
+               4. Wheat prices for 1996-97 includes a Central bonus of ₹ 60 per quintal payable up to June 30, 1997.
+               5. Wheat prices for 2005-06 and 2010-11 include a bonus of ₹ 50 per quintal payable over the MSP.
+               6. Paddy common for 2006-07 include an additional incentive bonus of ₹ 40 per quintal on procurement between October 1,
+                  2006 to March 31, 2007.
+               7. Arhar, Moong and Urad for 2007-08 includes a bonus of ₹ 40 per quintal payable over and above the MSP.
+               8. An additional incentive bonus of ₹ 50 per quintal over the MSP included for paddy common for the years 2008-09 and
+                  2009-10.
+               9. For Arhar, Moong and Urad for 2010-11 and 2011-12 an additional incentive at the rate of ₹ 500 per quintal payable during
+                   the harvest/arrival period of two months is included.
+               10. For Arhar, Moong and Urad for 2015-16 and 2017-18 bonus of ₹ 200 per quintal payable over and above the MSP.
+               11. Gram for 2015-16 includes a bonus of ₹ 75 for quintal and for 2017-18 includes a bonus of ₹ 150 per quintal on and above
+                   MSP and 2016-17 included a bonus of ₹ 200 per quintal.
+               12. Arhar, Moong and Urad for 2016-17 includes a bonus of ₹ 425 per quintal over and above MSP.
+                   Also See Notes on Tables.
+Sources : 1. Ministry of Agriculture &amp; Farmers Welfare, Government of India.
+                2. Commission for Agricultural Costs &amp; Prices (CACP).</t>
   </si>
 </sst>
 </file>
@@ -402,10 +405,10 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="4" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="2" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -423,17 +426,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:I62"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.6901" customWidth="1"/>
     <col min="3" max="9" width="18.1543293333333" customWidth="1"/>
+    <col min="10" max="10" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="17.0656" customHeight="1">
       <c r="B2" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
@@ -444,7 +448,7 @@
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="12.7992" customHeight="1">
       <c r="B4" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
@@ -505,10 +509,10 @@
         <v>8</v>
       </c>
       <c r="C8" s="5">
-        <v>2369</v>
+        <v>2441</v>
       </c>
       <c r="D8" s="5">
-        <v>2400</v>
+        <v>2410</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>9</v>
@@ -517,13 +521,13 @@
         <v>9</v>
       </c>
       <c r="G8" s="5">
-        <v>8000</v>
+        <v>8450</v>
       </c>
       <c r="H8" s="5">
-        <v>8768</v>
+        <v>8780</v>
       </c>
       <c r="I8" s="5">
-        <v>7800</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -531,25 +535,25 @@
         <v>10</v>
       </c>
       <c r="C9" s="7">
-        <v>2300</v>
+        <v>2369</v>
       </c>
       <c r="D9" s="7">
-        <v>2225</v>
+        <v>2400</v>
       </c>
       <c r="E9" s="7">
-        <v>2425</v>
+        <v>2585</v>
       </c>
       <c r="F9" s="7">
-        <v>5650</v>
+        <v>5875</v>
       </c>
       <c r="G9" s="7">
-        <v>7550</v>
+        <v>8000</v>
       </c>
       <c r="H9" s="7">
-        <v>8682</v>
+        <v>8768</v>
       </c>
       <c r="I9" s="7">
-        <v>7400</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -557,25 +561,25 @@
         <v>11</v>
       </c>
       <c r="C10" s="5">
-        <v>2183</v>
+        <v>2300</v>
       </c>
       <c r="D10" s="5">
-        <v>2090</v>
+        <v>2225</v>
       </c>
       <c r="E10" s="5">
-        <v>2275</v>
+        <v>2425</v>
       </c>
       <c r="F10" s="5">
-        <v>5440</v>
+        <v>5650</v>
       </c>
       <c r="G10" s="5">
-        <v>7000</v>
+        <v>7550</v>
       </c>
       <c r="H10" s="5">
-        <v>8558</v>
+        <v>8682</v>
       </c>
       <c r="I10" s="5">
-        <v>6950</v>
+        <v>7400</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -583,25 +587,25 @@
         <v>12</v>
       </c>
       <c r="C11" s="7">
-        <v>2040</v>
+        <v>2183</v>
       </c>
       <c r="D11" s="7">
-        <v>1962</v>
+        <v>2090</v>
       </c>
       <c r="E11" s="7">
-        <v>2125</v>
+        <v>2275</v>
       </c>
       <c r="F11" s="7">
-        <v>5335</v>
+        <v>5440</v>
       </c>
       <c r="G11" s="7">
-        <v>6600</v>
+        <v>7000</v>
       </c>
       <c r="H11" s="7">
-        <v>7755</v>
+        <v>8558</v>
       </c>
       <c r="I11" s="7">
-        <v>6600</v>
+        <v>6950</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -609,25 +613,25 @@
         <v>13</v>
       </c>
       <c r="C12" s="5">
-        <v>1940</v>
+        <v>2040</v>
       </c>
       <c r="D12" s="5">
-        <v>1870</v>
+        <v>1962</v>
       </c>
       <c r="E12" s="5">
-        <v>2015</v>
+        <v>2125</v>
       </c>
       <c r="F12" s="5">
-        <v>5230</v>
+        <v>5335</v>
       </c>
       <c r="G12" s="5">
-        <v>6300</v>
+        <v>6600</v>
       </c>
       <c r="H12" s="5">
-        <v>7275</v>
+        <v>7755</v>
       </c>
       <c r="I12" s="5">
-        <v>6300</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -635,25 +639,25 @@
         <v>14</v>
       </c>
       <c r="C13" s="7">
-        <v>1868</v>
+        <v>1940</v>
       </c>
       <c r="D13" s="7">
-        <v>1850</v>
+        <v>1870</v>
       </c>
       <c r="E13" s="7">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="F13" s="7">
-        <v>5100</v>
+        <v>5230</v>
       </c>
       <c r="G13" s="7">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="H13" s="7">
-        <v>7196</v>
+        <v>7275</v>
       </c>
       <c r="I13" s="7">
-        <v>6000</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -661,25 +665,25 @@
         <v>15</v>
       </c>
       <c r="C14" s="5">
-        <v>1815</v>
+        <v>1868</v>
       </c>
       <c r="D14" s="5">
-        <v>1760</v>
+        <v>1850</v>
       </c>
       <c r="E14" s="5">
-        <v>1925</v>
+        <v>1975</v>
       </c>
       <c r="F14" s="5">
-        <v>4875</v>
+        <v>5100</v>
       </c>
       <c r="G14" s="5">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="H14" s="5">
-        <v>7050</v>
+        <v>7196</v>
       </c>
       <c r="I14" s="5">
-        <v>5700</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -687,25 +691,25 @@
         <v>16</v>
       </c>
       <c r="C15" s="7">
-        <v>1750</v>
+        <v>1815</v>
       </c>
       <c r="D15" s="7">
-        <v>1700</v>
+        <v>1760</v>
       </c>
       <c r="E15" s="7">
-        <v>1840</v>
+        <v>1925</v>
       </c>
       <c r="F15" s="7">
-        <v>4620</v>
+        <v>4875</v>
       </c>
       <c r="G15" s="7">
-        <v>5675</v>
+        <v>5800</v>
       </c>
       <c r="H15" s="7">
-        <v>6975</v>
+        <v>7050</v>
       </c>
       <c r="I15" s="7">
-        <v>5600</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -713,25 +717,25 @@
         <v>17</v>
       </c>
       <c r="C16" s="5">
-        <v>1550</v>
+        <v>1750</v>
       </c>
       <c r="D16" s="5">
-        <v>1425</v>
+        <v>1700</v>
       </c>
       <c r="E16" s="5">
-        <v>1735</v>
+        <v>1840</v>
       </c>
       <c r="F16" s="5">
-        <v>4400</v>
+        <v>4620</v>
       </c>
       <c r="G16" s="5">
-        <v>5450</v>
+        <v>5675</v>
       </c>
       <c r="H16" s="5">
-        <v>5575</v>
+        <v>6975</v>
       </c>
       <c r="I16" s="5">
-        <v>5400</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -739,25 +743,25 @@
         <v>18</v>
       </c>
       <c r="C17" s="7">
-        <v>1470</v>
+        <v>1550</v>
       </c>
       <c r="D17" s="7">
-        <v>1365</v>
+        <v>1425</v>
       </c>
       <c r="E17" s="7">
-        <v>1625</v>
+        <v>1735</v>
       </c>
       <c r="F17" s="7">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="G17" s="7">
-        <v>5050</v>
+        <v>5450</v>
       </c>
       <c r="H17" s="7">
-        <v>5225</v>
+        <v>5575</v>
       </c>
       <c r="I17" s="7">
-        <v>5000</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -765,25 +769,25 @@
         <v>19</v>
       </c>
       <c r="C18" s="5">
-        <v>1410</v>
+        <v>1470</v>
       </c>
       <c r="D18" s="5">
-        <v>1325</v>
+        <v>1365</v>
       </c>
       <c r="E18" s="5">
-        <v>1525</v>
+        <v>1625</v>
       </c>
       <c r="F18" s="5">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="G18" s="5">
-        <v>4625</v>
+        <v>5050</v>
       </c>
       <c r="H18" s="5">
-        <v>4850</v>
+        <v>5225</v>
       </c>
       <c r="I18" s="5">
-        <v>4625</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -791,25 +795,25 @@
         <v>20</v>
       </c>
       <c r="C19" s="7">
-        <v>1360</v>
+        <v>1410</v>
       </c>
       <c r="D19" s="7">
-        <v>1310</v>
+        <v>1325</v>
       </c>
       <c r="E19" s="7">
-        <v>1450</v>
+        <v>1525</v>
       </c>
       <c r="F19" s="7">
-        <v>3175</v>
+        <v>3500</v>
       </c>
       <c r="G19" s="7">
-        <v>4350</v>
+        <v>4625</v>
       </c>
       <c r="H19" s="7">
-        <v>4600</v>
+        <v>4850</v>
       </c>
       <c r="I19" s="7">
-        <v>4350</v>
+        <v>4625</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -817,25 +821,25 @@
         <v>21</v>
       </c>
       <c r="C20" s="5">
-        <v>1310</v>
+        <v>1360</v>
       </c>
       <c r="D20" s="5">
         <v>1310</v>
       </c>
       <c r="E20" s="5">
-        <v>1400</v>
+        <v>1450</v>
       </c>
       <c r="F20" s="5">
-        <v>3100</v>
+        <v>3175</v>
       </c>
       <c r="G20" s="5">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="H20" s="5">
-        <v>4500</v>
+        <v>4600</v>
       </c>
       <c r="I20" s="5">
-        <v>4300</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -843,22 +847,22 @@
         <v>22</v>
       </c>
       <c r="C21" s="7">
-        <v>1250</v>
+        <v>1310</v>
       </c>
       <c r="D21" s="7">
-        <v>1175</v>
+        <v>1310</v>
       </c>
       <c r="E21" s="7">
-        <v>1350</v>
+        <v>1400</v>
       </c>
       <c r="F21" s="7">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G21" s="7">
-        <v>3850</v>
+        <v>4300</v>
       </c>
       <c r="H21" s="7">
-        <v>4400</v>
+        <v>4500</v>
       </c>
       <c r="I21" s="7">
         <v>4300</v>
@@ -869,25 +873,25 @@
         <v>23</v>
       </c>
       <c r="C22" s="5">
-        <v>1080</v>
+        <v>1250</v>
       </c>
       <c r="D22" s="5">
-        <v>980</v>
+        <v>1175</v>
       </c>
       <c r="E22" s="5">
-        <v>1285</v>
+        <v>1350</v>
       </c>
       <c r="F22" s="5">
-        <v>2800</v>
+        <v>3000</v>
       </c>
       <c r="G22" s="5">
-        <v>3700</v>
+        <v>3850</v>
       </c>
       <c r="H22" s="5">
-        <v>4000</v>
+        <v>4400</v>
       </c>
       <c r="I22" s="5">
-        <v>3800</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -895,25 +899,25 @@
         <v>24</v>
       </c>
       <c r="C23" s="7">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="D23" s="7">
-        <v>880</v>
+        <v>980</v>
       </c>
       <c r="E23" s="7">
-        <v>1170</v>
+        <v>1285</v>
       </c>
       <c r="F23" s="7">
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="G23" s="7">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="H23" s="7">
-        <v>3670</v>
+        <v>4000</v>
       </c>
       <c r="I23" s="7">
-        <v>3400</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -921,25 +925,25 @@
         <v>25</v>
       </c>
       <c r="C24" s="5">
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="D24" s="5">
-        <v>840</v>
+        <v>880</v>
       </c>
       <c r="E24" s="5">
-        <v>1100</v>
+        <v>1170</v>
       </c>
       <c r="F24" s="5">
-        <v>1760</v>
+        <v>2100</v>
       </c>
       <c r="G24" s="5">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="H24" s="5">
-        <v>2760</v>
+        <v>3670</v>
       </c>
       <c r="I24" s="5">
-        <v>2520</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -947,22 +951,22 @@
         <v>26</v>
       </c>
       <c r="C25" s="7">
-        <v>900</v>
+        <v>1050</v>
       </c>
       <c r="D25" s="7">
         <v>840</v>
       </c>
       <c r="E25" s="7">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="F25" s="7">
-        <v>1730</v>
+        <v>1760</v>
       </c>
       <c r="G25" s="7">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="H25" s="7">
-        <v>2520</v>
+        <v>2760</v>
       </c>
       <c r="I25" s="7">
         <v>2520</v>
@@ -973,25 +977,25 @@
         <v>27</v>
       </c>
       <c r="C26" s="5">
-        <v>745</v>
+        <v>900</v>
       </c>
       <c r="D26" s="5">
-        <v>620</v>
+        <v>840</v>
       </c>
       <c r="E26" s="5">
-        <v>1000</v>
+        <v>1080</v>
       </c>
       <c r="F26" s="5">
-        <v>1600</v>
+        <v>1730</v>
       </c>
       <c r="G26" s="5">
-        <v>1550</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="5">
-        <v>1700</v>
+        <v>2520</v>
       </c>
       <c r="I26" s="5">
-        <v>1700</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -999,25 +1003,25 @@
         <v>28</v>
       </c>
       <c r="C27" s="7">
-        <v>580</v>
+        <v>745</v>
       </c>
       <c r="D27" s="7">
-        <v>540</v>
+        <v>620</v>
       </c>
       <c r="E27" s="7">
-        <v>850</v>
+        <v>1000</v>
       </c>
       <c r="F27" s="7">
-        <v>1445</v>
+        <v>1600</v>
       </c>
       <c r="G27" s="7">
-        <v>1410</v>
+        <v>1550</v>
       </c>
       <c r="H27" s="7">
-        <v>1520</v>
+        <v>1700</v>
       </c>
       <c r="I27" s="7">
-        <v>1520</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1025,19 +1029,19 @@
         <v>29</v>
       </c>
       <c r="C28" s="5">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="D28" s="5">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="E28" s="5">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="F28" s="5">
-        <v>1435</v>
+        <v>1445</v>
       </c>
       <c r="G28" s="5">
-        <v>1400</v>
+        <v>1410</v>
       </c>
       <c r="H28" s="5">
         <v>1520</v>
@@ -1051,25 +1055,25 @@
         <v>30</v>
       </c>
       <c r="C29" s="7">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="D29" s="7">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="E29" s="7">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="F29" s="7">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="G29" s="7">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="H29" s="7">
-        <v>1410</v>
+        <v>1520</v>
       </c>
       <c r="I29" s="7">
-        <v>1410</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1077,25 +1081,25 @@
         <v>31</v>
       </c>
       <c r="C30" s="5">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="D30" s="5">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="E30" s="5">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="F30" s="5">
-        <v>1400</v>
+        <v>1425</v>
       </c>
       <c r="G30" s="5">
-        <v>1360</v>
+        <v>1390</v>
       </c>
       <c r="H30" s="5">
-        <v>1370</v>
+        <v>1410</v>
       </c>
       <c r="I30" s="5">
-        <v>1370</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1103,25 +1107,25 @@
         <v>32</v>
       </c>
       <c r="C31" s="7">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="D31" s="7">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="E31" s="7">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="F31" s="7">
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="G31" s="7">
-        <v>1320</v>
+        <v>1360</v>
       </c>
       <c r="H31" s="7">
-        <v>1330</v>
+        <v>1370</v>
       </c>
       <c r="I31" s="7">
-        <v>1330</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1138,16 +1142,16 @@
         <v>620</v>
       </c>
       <c r="F32" s="5">
-        <v>1200</v>
+        <v>1220</v>
       </c>
       <c r="G32" s="5">
         <v>1320</v>
       </c>
       <c r="H32" s="5">
-        <v>1320</v>
+        <v>1330</v>
       </c>
       <c r="I32" s="5">
-        <v>1320</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1155,25 +1159,25 @@
         <v>34</v>
       </c>
       <c r="C33" s="7">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="D33" s="7">
-        <v>445</v>
+        <v>485</v>
       </c>
       <c r="E33" s="7">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="F33" s="7">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="G33" s="7">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="H33" s="7">
-        <v>1200</v>
+        <v>1320</v>
       </c>
       <c r="I33" s="7">
-        <v>1200</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1181,25 +1185,25 @@
         <v>35</v>
       </c>
       <c r="C34" s="5">
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="D34" s="5">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="E34" s="5">
-        <v>580</v>
+        <v>610</v>
       </c>
       <c r="F34" s="5">
-        <v>1015</v>
+        <v>1100</v>
       </c>
       <c r="G34" s="5">
-        <v>1105</v>
+        <v>1200</v>
       </c>
       <c r="H34" s="5">
-        <v>1105</v>
+        <v>1200</v>
       </c>
       <c r="I34" s="5">
-        <v>1105</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1207,25 +1211,25 @@
         <v>36</v>
       </c>
       <c r="C35" s="7">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="D35" s="7">
-        <v>390</v>
+        <v>415</v>
       </c>
       <c r="E35" s="7">
-        <v>550</v>
+        <v>580</v>
       </c>
       <c r="F35" s="7">
-        <v>895</v>
+        <v>1015</v>
       </c>
       <c r="G35" s="7">
-        <v>960</v>
+        <v>1105</v>
       </c>
       <c r="H35" s="7">
-        <v>960</v>
+        <v>1105</v>
       </c>
       <c r="I35" s="7">
-        <v>960</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1233,25 +1237,25 @@
         <v>37</v>
       </c>
       <c r="C36" s="5">
-        <v>415</v>
+        <v>440</v>
       </c>
       <c r="D36" s="5">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="E36" s="5">
-        <v>510</v>
+        <v>550</v>
       </c>
       <c r="F36" s="5">
-        <v>815</v>
+        <v>895</v>
       </c>
       <c r="G36" s="5">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="H36" s="5">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="I36" s="5">
-        <v>900</v>
+        <v>960</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1259,25 +1263,25 @@
         <v>38</v>
       </c>
       <c r="C37" s="7">
-        <v>380</v>
+        <v>415</v>
       </c>
       <c r="D37" s="7">
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="E37" s="7">
-        <v>475</v>
+        <v>510</v>
       </c>
       <c r="F37" s="7">
-        <v>740</v>
+        <v>815</v>
       </c>
       <c r="G37" s="7">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="H37" s="7">
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="I37" s="7">
-        <v>840</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1285,25 +1289,25 @@
         <v>39</v>
       </c>
       <c r="C38" s="5">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="D38" s="5">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E38" s="5">
-        <v>380</v>
+        <v>475</v>
       </c>
       <c r="F38" s="5">
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="G38" s="5">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="H38" s="5">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="I38" s="5">
-        <v>800</v>
+        <v>840</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1311,25 +1315,25 @@
         <v>40</v>
       </c>
       <c r="C39" s="7">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="D39" s="7">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="E39" s="7">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="F39" s="7">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="G39" s="7">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="H39" s="7">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="I39" s="7">
-        <v>760</v>
+        <v>800</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1337,25 +1341,25 @@
         <v>41</v>
       </c>
       <c r="C40" s="5">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="D40" s="5">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E40" s="5">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="F40" s="5">
-        <v>640</v>
+        <v>670</v>
       </c>
       <c r="G40" s="5">
-        <v>700</v>
+        <v>760</v>
       </c>
       <c r="H40" s="5">
-        <v>700</v>
+        <v>760</v>
       </c>
       <c r="I40" s="5">
-        <v>700</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1363,25 +1367,25 @@
         <v>42</v>
       </c>
       <c r="C41" s="7">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="D41" s="7">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E41" s="7">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="F41" s="7">
-        <v>600</v>
+        <v>640</v>
       </c>
       <c r="G41" s="7">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="H41" s="7">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="I41" s="7">
-        <v>640</v>
+        <v>700</v>
       </c>
     </row>
     <row r="42" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1389,25 +1393,25 @@
         <v>43</v>
       </c>
       <c r="C42" s="5">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="D42" s="5">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="E42" s="5">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="F42" s="5">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G42" s="5">
-        <v>545</v>
+        <v>640</v>
       </c>
       <c r="H42" s="5">
-        <v>545</v>
+        <v>640</v>
       </c>
       <c r="I42" s="5">
-        <v>545</v>
+        <v>640</v>
       </c>
     </row>
     <row r="43" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1415,25 +1419,25 @@
         <v>44</v>
       </c>
       <c r="C43" s="7">
+        <v>230</v>
+      </c>
+      <c r="D43" s="7">
         <v>205</v>
       </c>
-      <c r="D43" s="7">
-        <v>180</v>
-      </c>
       <c r="E43" s="7">
-        <v>225</v>
+        <v>280</v>
       </c>
       <c r="F43" s="7">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="G43" s="7">
-        <v>480</v>
+        <v>545</v>
       </c>
       <c r="H43" s="7">
-        <v>480</v>
+        <v>545</v>
       </c>
       <c r="I43" s="7">
-        <v>480</v>
+        <v>545</v>
       </c>
     </row>
     <row r="44" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1441,25 +1445,25 @@
         <v>45</v>
       </c>
       <c r="C44" s="5">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="D44" s="5">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="E44" s="5">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F44" s="5">
-        <v>421</v>
+        <v>450</v>
       </c>
       <c r="G44" s="5">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="H44" s="5">
-        <v>425</v>
+        <v>480</v>
       </c>
       <c r="I44" s="5">
-        <v>425</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1467,25 +1471,25 @@
         <v>46</v>
       </c>
       <c r="C45" s="7">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="D45" s="7">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E45" s="7">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="F45" s="7">
-        <v>325</v>
+        <v>421</v>
       </c>
       <c r="G45" s="7">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="H45" s="7">
-        <v>360</v>
+        <v>425</v>
       </c>
       <c r="I45" s="7">
-        <v>360</v>
+        <v>425</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1493,25 +1497,25 @@
         <v>47</v>
       </c>
       <c r="C46" s="5">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="D46" s="5">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E46" s="5">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F46" s="5">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="G46" s="5">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="H46" s="5">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="I46" s="5">
-        <v>325</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1519,25 +1523,25 @@
         <v>48</v>
       </c>
       <c r="C47" s="7">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D47" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E47" s="7">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F47" s="7">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G47" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H47" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="I47" s="7">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1545,25 +1549,25 @@
         <v>49</v>
       </c>
       <c r="C48" s="5">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D48" s="5">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E48" s="5">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F48" s="5">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="G48" s="5">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="H48" s="5">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="I48" s="5">
-        <v>300</v>
+        <v>320</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1571,25 +1575,25 @@
         <v>50</v>
       </c>
       <c r="C49" s="7">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D49" s="7">
         <v>130</v>
       </c>
       <c r="E49" s="7">
-        <v>157</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>9</v>
+        <v>162</v>
+      </c>
+      <c r="F49" s="7">
+        <v>260</v>
       </c>
       <c r="G49" s="7">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="H49" s="7">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="I49" s="7">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1597,25 +1601,25 @@
         <v>51</v>
       </c>
       <c r="C50" s="5">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D50" s="5">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E50" s="5">
-        <v>152</v>
-      </c>
-      <c r="F50" s="5">
-        <v>240</v>
+        <v>157</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="G50" s="5">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="H50" s="5">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="I50" s="5">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1623,25 +1627,25 @@
         <v>52</v>
       </c>
       <c r="C51" s="7">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D51" s="7">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E51" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F51" s="7">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="G51" s="7">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="H51" s="7">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="I51" s="7">
-        <v>230</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1649,25 +1653,25 @@
         <v>53</v>
       </c>
       <c r="C52" s="5">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D52" s="5">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E52" s="5">
-        <v>142</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>9</v>
+        <v>151</v>
+      </c>
+      <c r="F52" s="5">
+        <v>235</v>
+      </c>
+      <c r="G52" s="5">
+        <v>215</v>
+      </c>
+      <c r="H52" s="5">
+        <v>240</v>
+      </c>
+      <c r="I52" s="5">
+        <v>230</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1675,25 +1679,25 @@
         <v>54</v>
       </c>
       <c r="C53" s="7">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D53" s="7">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="E53" s="7">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G53" s="7">
-        <v>190</v>
-      </c>
-      <c r="H53" s="7">
-        <v>200</v>
-      </c>
-      <c r="I53" s="7">
-        <v>200</v>
+      <c r="G53" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1701,25 +1705,25 @@
         <v>55</v>
       </c>
       <c r="C54" s="5">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D54" s="5">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E54" s="5">
-        <v>117</v>
-      </c>
-      <c r="F54" s="5">
-        <v>145</v>
+        <v>130</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="G54" s="5">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="H54" s="5">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
-        <v>175</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1727,25 +1731,25 @@
         <v>56</v>
       </c>
       <c r="C55" s="7">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D55" s="7">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E55" s="7">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F55" s="7">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G55" s="7">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="H55" s="7">
-        <v>165</v>
-      </c>
-      <c r="I55" s="8" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="I55" s="7">
+        <v>175</v>
       </c>
     </row>
     <row r="56" s="1" customFormat="1" ht="14.3991" customHeight="1">
@@ -1753,22 +1757,22 @@
         <v>57</v>
       </c>
       <c r="C56" s="5">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D56" s="5">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E56" s="5">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F56" s="5">
-        <v>125</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>9</v>
+        <v>140</v>
+      </c>
+      <c r="G56" s="5">
+        <v>155</v>
+      </c>
+      <c r="H56" s="5">
+        <v>165</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>9</v>
@@ -1779,16 +1783,16 @@
         <v>58</v>
       </c>
       <c r="C57" s="7">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D57" s="7">
         <v>74</v>
       </c>
       <c r="E57" s="7">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F57" s="7">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="G57" s="8" t="s">
         <v>9</v>
@@ -1801,46 +1805,73 @@
       </c>
     </row>
     <row r="58" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="5">
         <v>74</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58" s="5">
         <v>74</v>
       </c>
-      <c r="E58" s="10">
+      <c r="E58" s="5">
+        <v>110</v>
+      </c>
+      <c r="F58" s="5">
+        <v>95</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="14.3991" customHeight="1">
+      <c r="B59" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59" s="10">
+        <v>74</v>
+      </c>
+      <c r="D59" s="10">
+        <v>74</v>
+      </c>
+      <c r="E59" s="10">
         <v>105</v>
       </c>
-      <c r="F58" s="10">
+      <c r="F59" s="10">
         <v>90</v>
       </c>
-      <c r="G58" s="11" t="s">
+      <c r="G59" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H59" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I58" s="11" t="s">
+      <c r="I59" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="60" s="1" customFormat="1" ht="255.984" customHeight="1">
-      <c r="B60" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-    </row>
+    <row r="60" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
+    <row r="61" s="1" customFormat="1" ht="255.984" customHeight="1">
+      <c r="B61" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
   </mergeCells>
   <pageSetup paperSize="8" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
